--- a/accor/data/concept_pilote.xlsx
+++ b/accor/data/concept_pilote.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,86 +413,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>hotel_code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>hotel_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>hotel_brand</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>annee</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>nb_chambres</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>taux_occupation</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>guests_per_chambre</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>clients_jour</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>clients_mois</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>n_mois_renseignes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ca_mensuel_moyen</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>n_produits_distincts_f_b</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>n_produits_distincts_n_f_b</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>n_produits_distincts_total</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>mix_f_b</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>mix_n_f_b</t>
         </is>
@@ -533,37 +521,37 @@
         <v>305</v>
       </c>
       <c r="F2" t="n">
-        <v>0.825</v>
+        <v>0.7</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>503.25</v>
+        <v>427</v>
       </c>
       <c r="I2" t="n">
-        <v>15349.125</v>
+        <v>13023.5</v>
       </c>
       <c r="J2" t="n">
         <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>5095.25</v>
+        <v>5908.7279</v>
       </c>
       <c r="L2" t="n">
         <v>69</v>
       </c>
       <c r="M2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O2" t="n">
-        <v>0.676471</v>
+        <v>0.669903</v>
       </c>
       <c r="P2" t="n">
-        <v>0.323529</v>
+        <v>0.330097</v>
       </c>
     </row>
     <row r="3">
@@ -589,37 +577,37 @@
         <v>305</v>
       </c>
       <c r="F3" t="n">
-        <v>0.825</v>
+        <v>0.7</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>503.25</v>
+        <v>427</v>
       </c>
       <c r="I3" t="n">
-        <v>15349.125</v>
+        <v>13023.5</v>
       </c>
       <c r="J3" t="n">
         <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>3536.4417</v>
+        <v>3759.1647</v>
       </c>
       <c r="L3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3" t="n">
         <v>22</v>
       </c>
       <c r="N3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O3" t="n">
-        <v>0.541667</v>
+        <v>0.55102</v>
       </c>
       <c r="P3" t="n">
-        <v>0.458333</v>
+        <v>0.44898</v>
       </c>
     </row>
     <row r="4">
@@ -645,22 +633,22 @@
         <v>305</v>
       </c>
       <c r="F4" t="n">
-        <v>0.825</v>
+        <v>0.7</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>503.25</v>
+        <v>427</v>
       </c>
       <c r="I4" t="n">
-        <v>15349.125</v>
+        <v>13023.5</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>2685.95</v>
+        <v>2709.4313</v>
       </c>
       <c r="L4" t="n">
         <v>22</v>
@@ -681,236 +669,236 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H2075</t>
+          <t>H0438</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ibis budget Nice Californie</t>
+          <t>Novotel Mâcon Nord - Porte de Bourgogne</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IBIS BUDGET</t>
+          <t>NOVOTEL</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E5" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.825</v>
+        <v>0.7</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H5" t="n">
-        <v>180.9225</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>5518.1362</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>253</v>
+        <v>970.0273</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M5" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.7727270000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0.227273</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H2075</t>
+          <t>H0438</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ibis budget Nice Californie</t>
+          <t>Novotel Mâcon Nord - Porte de Bourgogne</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IBIS BUDGET</t>
+          <t>NOVOTEL</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E6" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.825</v>
+        <v>0.7</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H6" t="n">
-        <v>180.9225</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>5518.1362</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>534.61</v>
+        <v>666.5659000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="M6" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="O6" t="n">
-        <v>0.329545</v>
+        <v>0.926471</v>
       </c>
       <c r="P6" t="n">
-        <v>0.670455</v>
+        <v>0.073529</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H2075</t>
+          <t>H0438</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ibis budget Nice Californie</t>
+          <t>Novotel Mâcon Nord - Porte de Bourgogne</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IBIS BUDGET</t>
+          <t>NOVOTEL</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E7" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.825</v>
+        <v>0.7</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>180.9225</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>5518.1362</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>1001.025</v>
+        <v>204.0292</v>
       </c>
       <c r="L7" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="M7" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="O7" t="n">
-        <v>0.320755</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0.679245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H2075</t>
+          <t>H1978</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ibis budget Nice Californie</t>
+          <t>Novotel Paris Vaugirard Montparnasse - Hôtel vue tour Eiffel |ALL - ALL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IBIS BUDGET</t>
+          <t>NOVOTEL</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="E8" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.825</v>
+        <v>0.7</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H8" t="n">
-        <v>180.9225</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>5518.1362</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>335.3</v>
+        <v>10240.47</v>
       </c>
       <c r="L8" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M8" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="N8" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="O8" t="n">
-        <v>0.510204</v>
+        <v>0.842697</v>
       </c>
       <c r="P8" t="n">
-        <v>0.489796</v>
+        <v>0.157303</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H3546</t>
+          <t>H1978</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Novotel Paris Centre Tour Eiffel</t>
+          <t>Novotel Paris Vaugirard Montparnasse - Hôtel vue tour Eiffel |ALL - ALL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -919,54 +907,54 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E9" t="n">
-        <v>764</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.825</v>
+        <v>0.7</v>
       </c>
       <c r="G9" t="n">
         <v>1.8</v>
       </c>
       <c r="H9" t="n">
-        <v>1134.54</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>34603.47</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>6786.7814</v>
+        <v>21994.7661</v>
       </c>
       <c r="L9" t="n">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="M9" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="N9" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="O9" t="n">
-        <v>0.850575</v>
+        <v>0.828125</v>
       </c>
       <c r="P9" t="n">
-        <v>0.149425</v>
+        <v>0.171875</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H3546</t>
+          <t>H1978</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Novotel Paris Centre Tour Eiffel</t>
+          <t>Novotel Paris Vaugirard Montparnasse - Hôtel vue tour Eiffel |ALL - ALL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -975,317 +963,317 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E10" t="n">
-        <v>764</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.825</v>
+        <v>0.7</v>
       </c>
       <c r="G10" t="n">
         <v>1.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1134.54</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>34603.47</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>15018.7917</v>
+        <v>9028.436799999999</v>
       </c>
       <c r="L10" t="n">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="M10" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="N10" t="n">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="O10" t="n">
-        <v>0.833333</v>
+        <v>0.802817</v>
       </c>
       <c r="P10" t="n">
-        <v>0.166667</v>
+        <v>0.197183</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H3546</t>
+          <t>H2075</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Novotel Paris Centre Tour Eiffel</t>
+          <t>Ibis budget Nice Californie</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NOVOTEL</t>
+          <t>IBIS BUDGET</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="E11" t="n">
-        <v>764</v>
+        <v>129</v>
       </c>
       <c r="F11" t="n">
-        <v>0.825</v>
+        <v>0.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H11" t="n">
-        <v>1134.54</v>
+        <v>153.51</v>
       </c>
       <c r="I11" t="n">
-        <v>34603.47</v>
+        <v>4682.055</v>
       </c>
       <c r="J11" t="n">
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>9518.375</v>
+        <v>203.3333</v>
       </c>
       <c r="L11" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="N11" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="O11" t="n">
-        <v>0.811594</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.188406</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HB5I0</t>
+          <t>H2075</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Novotel Megève Mont-Blanc</t>
+          <t>Ibis budget Nice Californie</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NOVOTEL</t>
+          <t>IBIS BUDGET</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>2024</v>
       </c>
       <c r="E12" t="n">
-        <v>572</v>
+        <v>129</v>
       </c>
       <c r="F12" t="n">
-        <v>0.825</v>
+        <v>0.7</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H12" t="n">
-        <v>849.42</v>
+        <v>153.51</v>
       </c>
       <c r="I12" t="n">
-        <v>25907.31</v>
+        <v>4682.055</v>
       </c>
       <c r="J12" t="n">
         <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>1244.94</v>
+        <v>456.5189</v>
       </c>
       <c r="L12" t="n">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="M12" t="n">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="N12" t="n">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="O12" t="n">
-        <v>0.385</v>
+        <v>0.358696</v>
       </c>
       <c r="P12" t="n">
-        <v>0.615</v>
+        <v>0.641304</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HB5I0</t>
+          <t>H2075</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Novotel Megève Mont-Blanc</t>
+          <t>Ibis budget Nice Californie</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NOVOTEL</t>
+          <t>IBIS BUDGET</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>2025</v>
       </c>
       <c r="E13" t="n">
-        <v>572</v>
+        <v>129</v>
       </c>
       <c r="F13" t="n">
-        <v>0.825</v>
+        <v>0.7</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H13" t="n">
-        <v>849.42</v>
+        <v>153.51</v>
       </c>
       <c r="I13" t="n">
-        <v>25907.31</v>
+        <v>4682.055</v>
       </c>
       <c r="J13" t="n">
         <v>12</v>
       </c>
       <c r="K13" t="n">
-        <v>1603.4833</v>
+        <v>843.1414</v>
       </c>
       <c r="L13" t="n">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="M13" t="n">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="N13" t="n">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="O13" t="n">
-        <v>0.326923</v>
+        <v>0.342105</v>
       </c>
       <c r="P13" t="n">
-        <v>0.673077</v>
+        <v>0.657895</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HB5I0</t>
+          <t>H2075</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Novotel Megève Mont-Blanc</t>
+          <t>Ibis budget Nice Californie</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NOVOTEL</t>
+          <t>IBIS BUDGET</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>2026</v>
       </c>
       <c r="E14" t="n">
-        <v>572</v>
+        <v>129</v>
       </c>
       <c r="F14" t="n">
-        <v>0.825</v>
+        <v>0.7</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H14" t="n">
-        <v>849.42</v>
+        <v>153.51</v>
       </c>
       <c r="I14" t="n">
-        <v>25907.31</v>
+        <v>4682.055</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>2290.7625</v>
+        <v>255.855</v>
       </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M14" t="n">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="N14" t="n">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="O14" t="n">
-        <v>0.12766</v>
+        <v>0.510204</v>
       </c>
       <c r="P14" t="n">
-        <v>0.87234</v>
+        <v>0.489796</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HB6A3</t>
+          <t>H6188</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ibis budget Strasbourg Centre République</t>
+          <t>Mercure Paris Boulogne</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IBIS BUDGET</t>
+          <t>MERCURE</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2024</v>
       </c>
       <c r="E15" t="n">
-        <v>97</v>
+        <v>191</v>
       </c>
       <c r="F15" t="n">
         <v>0.7</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>115.43</v>
+        <v>267.4</v>
       </c>
       <c r="I15" t="n">
-        <v>3520.615</v>
+        <v>8155.7</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>945.8333</v>
+        <v>1088.7803</v>
       </c>
       <c r="L15" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -1297,51 +1285,51 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HB6A3</t>
+          <t>H6188</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ibis budget Strasbourg Centre République</t>
+          <t>Mercure Paris Boulogne</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IBIS BUDGET</t>
+          <t>MERCURE</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2025</v>
       </c>
       <c r="E16" t="n">
-        <v>97</v>
+        <v>191</v>
       </c>
       <c r="F16" t="n">
         <v>0.7</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>115.43</v>
+        <v>267.4</v>
       </c>
       <c r="I16" t="n">
-        <v>3520.615</v>
+        <v>8155.7</v>
       </c>
       <c r="J16" t="n">
         <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>1137.875</v>
+        <v>1467.153</v>
       </c>
       <c r="L16" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -1353,56 +1341,392 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HB6A3</t>
+          <t>H6188</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ibis budget Strasbourg Centre République</t>
+          <t>Mercure Paris Boulogne</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IBIS BUDGET</t>
+          <t>MERCURE</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2026</v>
       </c>
       <c r="E17" t="n">
-        <v>97</v>
+        <v>191</v>
       </c>
       <c r="F17" t="n">
         <v>0.7</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>115.43</v>
+        <v>267.4</v>
       </c>
       <c r="I17" t="n">
-        <v>3520.615</v>
+        <v>8155.7</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>526.25</v>
+        <v>819.23</v>
       </c>
       <c r="L17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
       </c>
       <c r="P17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HB5I0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Novotel Megève Mont-Blanc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NOVOTEL</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E18" t="n">
+        <v>572</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>720.72</v>
+      </c>
+      <c r="I18" t="n">
+        <v>21981.96</v>
+      </c>
+      <c r="J18" t="n">
+        <v>10</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1167.4162</v>
+      </c>
+      <c r="L18" t="n">
+        <v>81</v>
+      </c>
+      <c r="M18" t="n">
+        <v>126</v>
+      </c>
+      <c r="N18" t="n">
+        <v>206</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.391304</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.608696</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HB5I0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Novotel Megève Mont-Blanc</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NOVOTEL</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E19" t="n">
+        <v>572</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>720.72</v>
+      </c>
+      <c r="I19" t="n">
+        <v>21981.96</v>
+      </c>
+      <c r="J19" t="n">
+        <v>12</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1700.701</v>
+      </c>
+      <c r="L19" t="n">
+        <v>91</v>
+      </c>
+      <c r="M19" t="n">
+        <v>126</v>
+      </c>
+      <c r="N19" t="n">
+        <v>216</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.419355</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.580645</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HB5I0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Novotel Megève Mont-Blanc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NOVOTEL</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E20" t="n">
+        <v>572</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>720.72</v>
+      </c>
+      <c r="I20" t="n">
+        <v>21981.96</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1887.0568</v>
+      </c>
+      <c r="L20" t="n">
+        <v>29</v>
+      </c>
+      <c r="M20" t="n">
+        <v>80</v>
+      </c>
+      <c r="N20" t="n">
+        <v>95</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.266055</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.733945</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HB6A3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ibis budget Strasbourg Centre République</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>IBIS BUDGET</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E21" t="n">
+        <v>97</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>115.43</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3520.615</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1247.1212</v>
+      </c>
+      <c r="L21" t="n">
+        <v>34</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>34</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HB6A3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ibis budget Strasbourg Centre République</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>IBIS BUDGET</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E22" t="n">
+        <v>97</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>115.43</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3520.615</v>
+      </c>
+      <c r="J22" t="n">
+        <v>12</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1450.9789</v>
+      </c>
+      <c r="L22" t="n">
+        <v>34</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>34</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HB6A3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ibis budget Strasbourg Centre République</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>IBIS BUDGET</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E23" t="n">
+        <v>97</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>115.43</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3520.615</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>566.4773</v>
+      </c>
+      <c r="L23" t="n">
+        <v>24</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>24</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
